--- a/Base_de_donnees/Fichiers_metadonnees/Remplissage_des_tables_des_personnes.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Remplissage_des_tables_des_personnes.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Personnes&amp;Responsable_fichier" sheetId="1" state="visible" r:id="rId3"/>
@@ -99,10 +99,10 @@
     <t xml:space="preserve">Referent/Collecteur  (R/C)</t>
   </si>
   <si>
-    <t xml:space="preserve">date_debut (si R)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_fin (si R)</t>
+    <t xml:space="preserve">date_debut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_fin</t>
   </si>
   <si>
     <t xml:space="preserve">HOBO_02</t>
@@ -134,7 +134,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -178,18 +178,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -233,7 +221,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -258,15 +246,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -457,11 +437,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.9"/>
@@ -617,11 +596,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.38"/>
@@ -650,7 +628,7 @@
       <c r="J1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -659,12 +637,12 @@
       <c r="C2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="6" t="n">
         <v>45747</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -675,7 +653,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -704,11 +682,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.87"/>
@@ -724,7 +701,7 @@
       <c r="C1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -732,7 +709,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
